--- a/artfynd/A 1318-2026 artfynd.xlsx
+++ b/artfynd/A 1318-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY169"/>
+  <dimension ref="A1:AZ169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -812,6 +817,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203914</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839468</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1043,6 +1058,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205376</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1168,6 +1188,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205377</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1293,6 +1318,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205378</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1418,6 +1448,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205379</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1543,6 +1578,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205380</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1668,6 +1708,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205327</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1798,6 +1843,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205329</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1907,6 +1957,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839588</t>
         </is>
       </c>
     </row>
@@ -2040,6 +2095,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203863</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2171,6 +2231,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203864</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2302,6 +2367,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203865</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2433,6 +2503,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205368</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2564,6 +2639,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205369</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2699,6 +2779,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205396</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2824,6 +2909,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205326</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2935,6 +3025,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839502</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3049,6 +3144,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839557</t>
         </is>
       </c>
     </row>
@@ -3182,6 +3282,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203871</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3313,6 +3418,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203872</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3449,6 +3559,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203873</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3575,6 +3690,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203874</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3696,6 +3816,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203875</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3822,6 +3947,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203876</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3958,6 +4088,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203877</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4084,6 +4219,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203878</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4205,6 +4345,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203879</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4331,6 +4476,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203881</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4457,6 +4607,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203882</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4578,6 +4733,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203883</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4699,6 +4859,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203884</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4825,6 +4990,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203885</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4946,6 +5116,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203886</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5072,6 +5247,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203887</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5198,6 +5378,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203888</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5329,6 +5514,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203889</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5460,6 +5650,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203890</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5591,6 +5786,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203891</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5717,6 +5917,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203892</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5843,6 +6048,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203893</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5974,6 +6184,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203894</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6123,6 +6338,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203895</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6254,6 +6474,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203896</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6385,6 +6610,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203897</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6516,6 +6746,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203898</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6647,6 +6882,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203899</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6796,6 +7036,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203900</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6927,6 +7172,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203901</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7058,6 +7308,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203902</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7189,6 +7444,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203903</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7320,6 +7580,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203904</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7441,6 +7706,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203905</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7567,6 +7837,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203906</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7688,6 +7963,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203907</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7819,6 +8099,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203908</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7950,6 +8235,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203909</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8085,6 +8375,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203910</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8216,6 +8511,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203911</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8337,6 +8637,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203912</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8463,6 +8768,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203913</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8584,6 +8894,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205387</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8723,6 +9038,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205388</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8862,6 +9182,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205389</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9001,6 +9326,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205390</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9122,6 +9452,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205391</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9253,6 +9588,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205392</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9374,6 +9714,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205393</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9495,6 +9840,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205394</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9626,6 +9976,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205395</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9747,6 +10102,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205325</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9878,6 +10238,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203866</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9989,6 +10354,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839586</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -10103,6 +10473,11 @@
       <c r="AY75" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839866</t>
         </is>
       </c>
     </row>
@@ -10236,6 +10611,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203867</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10367,6 +10747,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203868</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10498,6 +10883,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205370</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10629,6 +11019,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205371</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10760,6 +11155,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205372</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10886,6 +11286,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205373</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10997,6 +11402,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839491</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -11127,6 +11537,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203858</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -11257,6 +11672,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203859</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -11392,6 +11812,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203860</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -11527,6 +11952,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203861</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11638,6 +12068,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839492</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11754,6 +12189,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839507</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11865,6 +12305,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839587</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11981,6 +12426,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839865</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -12116,6 +12566,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203869</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -12250,6 +12705,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203862</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -12384,6 +12844,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205365</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -12495,6 +12960,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839458</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -12611,6 +13081,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839460</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -12722,6 +13197,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839476</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -12833,6 +13313,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839543</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12949,6 +13434,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839545</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -13060,6 +13550,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839553</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -13171,6 +13666,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839556</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -13287,6 +13787,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839564</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -13422,6 +13927,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203838</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -13557,6 +14067,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203839</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -13692,6 +14207,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203840</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -13827,6 +14347,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203841</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -13962,6 +14487,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203842</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -14097,6 +14627,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203843</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -14232,6 +14767,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203844</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -14367,6 +14907,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203845</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -14502,6 +15047,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203846</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -14637,6 +15187,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203847</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -14772,6 +15327,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203849</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -14907,6 +15467,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203850</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -15042,6 +15607,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203851</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -15177,6 +15747,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203852</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -15312,6 +15887,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203854</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -15447,6 +16027,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203855</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -15582,6 +16167,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131203856</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -15712,6 +16302,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205331</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -15842,6 +16437,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205332</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -15972,6 +16572,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205333</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -16102,6 +16707,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205334</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -16232,6 +16842,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205335</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -16362,6 +16977,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205336</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -16492,6 +17112,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205337</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -16622,6 +17247,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205338</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -16752,6 +17382,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205339</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -16882,6 +17517,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205340</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -17012,6 +17652,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205341</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -17142,6 +17787,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205342</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -17289,6 +17939,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205343</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -17419,6 +18074,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205344</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -17549,6 +18209,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205345</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -17679,6 +18344,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205346</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -17809,6 +18479,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205347</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -17939,6 +18614,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205348</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -18069,6 +18749,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205349</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -18199,6 +18884,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205350</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -18329,6 +19019,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205351</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -18459,6 +19154,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205352</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -18589,6 +19289,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205353</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -18719,6 +19424,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205354</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -18849,6 +19559,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205355</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -18979,6 +19694,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205356</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -19109,6 +19829,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205357</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -19239,6 +19964,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205358</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -19369,6 +20099,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205359</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -19499,6 +20234,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205360</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -19634,6 +20374,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205361</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -19764,6 +20509,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205362</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -19894,6 +20644,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205363</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -20000,6 +20755,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839532</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -20128,6 +20888,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205375</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -20251,6 +21016,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205367</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -20357,6 +21127,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839589</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -20463,6 +21238,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839496</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -20574,6 +21354,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839523</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -20685,6 +21470,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839593</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -20796,6 +21586,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90921838</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -20907,6 +21702,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839519</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -21018,6 +21818,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839522</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -21129,6 +21934,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90921837</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -21240,6 +22050,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839467</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -21349,6 +22164,11 @@
       <c r="AY164" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839489</t>
         </is>
       </c>
     </row>
@@ -21462,6 +22282,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839499</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -21573,6 +22398,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839594</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -21684,6 +22514,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839524</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -21793,6 +22628,11 @@
       <c r="AY168" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90921839</t>
         </is>
       </c>
     </row>
@@ -21916,8 +22756,183 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205374</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>